--- a/DOC/基本設計書/ソフトウェア仕様書_別紙1_ソフトウェア構成図.xlsx
+++ b/DOC/基本設計書/ソフトウェア仕様書_別紙1_ソフトウェア構成図.xlsx
@@ -1,28 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abbbb\Todo_Java_Swing\DOC\基本設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B71E20-7B3B-47A9-9DE8-F61EDA94969B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D476314F-A1F0-475B-966C-9FE89C48274C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{8483CCA3-FAB1-9041-83F7-C09BCB54721B}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="888" firstSheet="4" activeTab="6" xr2:uid="{8483CCA3-FAB1-9041-83F7-C09BCB54721B}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
     <sheet name="1_画面遷移フロー" sheetId="3" r:id="rId2"/>
     <sheet name="2_画面構成図" sheetId="4" r:id="rId3"/>
     <sheet name="3_画面デザインパターン" sheetId="5" r:id="rId4"/>
-    <sheet name="4_画面更新指示通知" sheetId="6" r:id="rId5"/>
+    <sheet name="3_画面デザインパターン(LMStudio)" sheetId="7" r:id="rId5"/>
+    <sheet name="4_画面更新指示通知" sheetId="6" r:id="rId6"/>
+    <sheet name="5_ソフトウェアデザインパターン" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'1_画面遷移フロー'!$A$1:$AD$36</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'3_画面デザインパターン'!$A$1:$W$101</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'4_画面更新指示通知'!$A$1:$AE$104</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'3_画面デザインパターン(LMStudio)'!$A$1:$U$48</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'4_画面更新指示通知'!$A$1:$AE$104</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'5_ソフトウェアデザインパターン'!$A$1:$N$39</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="139">
   <si>
     <t>View層</t>
     <rPh sb="0" eb="1">
@@ -841,12 +845,207 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>リスト・タスク自動生成画面</t>
+    <rPh sb="11" eb="13">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リスト・タスク自動生成コントロール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>指示文言入力欄</t>
+    <rPh sb="0" eb="4">
+      <t>シジモンゴン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ニュウリョクラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リスト＋タスク生成ボタン</t>
+    <rPh sb="7" eb="9">
+      <t>セイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレビューパネル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面モデル</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TodoProcess</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LMStudio接続クライアント</t>
+    <rPh sb="8" eb="10">
+      <t>セツゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>指示文言入力</t>
+    <rPh sb="0" eb="4">
+      <t>シジモンゴン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボタン押下</t>
+    <rPh sb="3" eb="5">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボタン押下を受信</t>
+    <rPh sb="3" eb="5">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジュシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>生成処理リクエスト</t>
+    <rPh sb="0" eb="4">
+      <t>セイセイショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面配下の要素に対し非活性</t>
+    <rPh sb="0" eb="4">
+      <t>ガメンハイカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カッセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LLMへ生成依頼</t>
+    <rPh sb="4" eb="6">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イライ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>応答結果受信（JSON）</t>
+    <rPh sb="0" eb="4">
+      <t>オウトウケッカ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジュシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JSONをシリアライズする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>応答結果を画面型に変換</t>
+    <rPh sb="0" eb="4">
+      <t>オウトウケッカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヘンカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>生成処理レスポンス</t>
+    <rPh sb="0" eb="4">
+      <t>セイセイショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>応答結果を画面表示指示</t>
+    <rPh sb="0" eb="4">
+      <t>オウトウケッカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面配下の要素に対し活性</t>
+    <rPh sb="0" eb="4">
+      <t>ガメンハイカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カッセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>応答結果を画面表示</t>
+    <rPh sb="0" eb="4">
+      <t>オウトウケッカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -908,6 +1107,15 @@
       <color rgb="FFFF0000"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -1072,7 +1280,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1139,6 +1347,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1186,6 +1409,39 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5083,6 +5339,974 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="直線矢印コネクタ 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F04FF75-4A5F-4274-904C-BCD744643B97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="2368550"/>
+          <a:ext cx="939800" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>939800</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="直線矢印コネクタ 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37CBDBCB-14D7-4A36-844E-AFACC7A0B637}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="2616200"/>
+          <a:ext cx="939800" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="sysDash"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>941294</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="直線矢印コネクタ 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C917A00C-8C5D-4D66-9F4F-3C4F1DBA0B11}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="952500" y="4210050"/>
+          <a:ext cx="5008469" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>11206</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="直線矢印コネクタ 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B979C2BD-8B6D-42E3-A985-494A019F28DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="952500" y="4468906"/>
+          <a:ext cx="7059706" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>11206</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="直線矢印コネクタ 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E4C8ACF-F2A0-4101-8538-0A651BD889C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3821206" y="5448300"/>
+          <a:ext cx="9066119" cy="11206"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>11206</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>33618</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="直線矢印コネクタ 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A449CE5-E6C1-47DF-813D-3CB99BFAFE67}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3821206" y="5943600"/>
+          <a:ext cx="9066119" cy="33618"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EEA678C-8A33-45B0-BF9D-5CEDB7D13709}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15744825" y="6686550"/>
+          <a:ext cx="1905000" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="sysDash"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="直線矢印コネクタ 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2B020C0-F942-44B2-9048-1462389AB294}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17649825" y="7181850"/>
+          <a:ext cx="2028825" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="sysDash"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="直線矢印コネクタ 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC403615-4638-46E7-9B39-A2E0D341320F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="17649825" y="7677150"/>
+          <a:ext cx="2028825" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="sysDash"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="直線矢印コネクタ 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E4650A9-20DB-4DF3-A29D-84B0FE08BD54}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="15744825" y="8420100"/>
+          <a:ext cx="1905000" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="sysDash"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>941292</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>11206</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>224118</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="右中かっこ 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB270BA5-4EC4-4318-808F-8AE7BBE9453A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17638617" y="7677150"/>
+          <a:ext cx="974914" cy="719418"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightBrace">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 34783"/>
+            <a:gd name="adj2" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln w="28575"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="直線矢印コネクタ 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DBE8159-D24D-48AC-A62A-C73490AAFB6A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="12887325" y="8915400"/>
+          <a:ext cx="2857500" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>941294</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>33618</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="14" name="直線矢印コネクタ 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C4CB95D-0B4C-4055-B29D-A9A423EF7BC1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3810000" y="9906000"/>
+          <a:ext cx="9066119" cy="33618"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>33618</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>235323</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>22412</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="直線矢印コネクタ 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B015521B-8720-4708-B254-5C3DB8E97B6F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3843618" y="4940673"/>
+          <a:ext cx="4179794" cy="23533"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>941294</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="16" name="直線矢印コネクタ 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B97EC22D-F384-4D90-808C-1861EF08AC46}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3810000" y="10896600"/>
+          <a:ext cx="6208619" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>941294</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>33618</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="直線矢印コネクタ 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB9C2634-D725-47B4-97CD-0D4E40D735D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3810000" y="10401300"/>
+          <a:ext cx="9066119" cy="33618"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="18" name="直線矢印コネクタ 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27F5C448-99BD-4D55-9984-F088ACA7AB00}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12887325" y="6191250"/>
+          <a:ext cx="2857500" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>939800</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
         <xdr:cNvPr id="29" name="直線矢印コネクタ 28">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
@@ -7123,6 +8347,55 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>680357</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>219829</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA1F8625-DDE9-6040-933D-B68C323D2D1F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="762000" y="244929"/>
+          <a:ext cx="9062357" cy="9037257"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -7426,19 +8699,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C87D99CD-4C20-F24B-9433-B1D69E739214}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="20" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="11.109375" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="4.69140625" customWidth="1"/>
-    <col min="2" max="2" width="19.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.69140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -7449,7 +8722,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="13">
         <v>1</v>
       </c>
@@ -7460,7 +8733,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="13">
         <v>2</v>
       </c>
@@ -7471,7 +8744,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="13">
         <v>3</v>
       </c>
@@ -7482,7 +8755,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="13">
         <v>4</v>
       </c>
@@ -7503,464 +8776,464 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C7F4906-62F4-2D4E-BF9D-4EACD53A2029}">
   <dimension ref="A1:AA35"/>
-  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="20" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="11.109375" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="6.53515625" customWidth="1"/>
+    <col min="1" max="2" width="6.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.6">
-      <c r="C6" s="22" t="s">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="C6" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="P6" s="22" t="s">
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="P6" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="Q6" s="22"/>
-      <c r="R6" s="22"/>
-      <c r="S6" s="22"/>
-      <c r="T6" s="22"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="27"/>
+      <c r="S6" s="27"/>
+      <c r="T6" s="27"/>
       <c r="U6" s="21"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.6">
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23"/>
-      <c r="T7" s="23"/>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="28"/>
+      <c r="R7" s="28"/>
+      <c r="S7" s="28"/>
+      <c r="T7" s="28"/>
       <c r="U7" s="21"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.6">
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
-      <c r="T8" s="23"/>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="28"/>
+      <c r="S8" s="28"/>
+      <c r="T8" s="28"/>
       <c r="U8" s="21"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.6">
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="23"/>
-      <c r="T9" s="23"/>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
+      <c r="T9" s="28"/>
       <c r="U9" s="21"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.6">
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="23"/>
-      <c r="T10" s="23"/>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="P10" s="28"/>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="28"/>
+      <c r="S10" s="28"/>
+      <c r="T10" s="28"/>
       <c r="U10" s="21"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.6">
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
-      <c r="S11" s="23"/>
-      <c r="T11" s="23"/>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="P11" s="28"/>
+      <c r="Q11" s="28"/>
+      <c r="R11" s="28"/>
+      <c r="S11" s="28"/>
+      <c r="T11" s="28"/>
       <c r="U11" s="21"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.6">
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
-      <c r="S12" s="23"/>
-      <c r="T12" s="23"/>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="28"/>
+      <c r="S12" s="28"/>
+      <c r="T12" s="28"/>
       <c r="U12" s="21"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.6">
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="P13" s="28"/>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="28"/>
+      <c r="S13" s="28"/>
+      <c r="T13" s="28"/>
       <c r="U13" s="21"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.6">
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="P14" s="28"/>
+      <c r="Q14" s="28"/>
+      <c r="R14" s="28"/>
+      <c r="S14" s="28"/>
+      <c r="T14" s="28"/>
       <c r="U14" s="21"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.6">
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
-      <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="28"/>
+      <c r="R15" s="28"/>
+      <c r="S15" s="28"/>
+      <c r="T15" s="28"/>
       <c r="U15" s="21"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.6">
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
-      <c r="S16" s="23"/>
-      <c r="T16" s="23"/>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28"/>
       <c r="U16" s="21"/>
     </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.6">
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
-      <c r="S17" s="23"/>
-      <c r="T17" s="23"/>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.4">
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="P17" s="28"/>
+      <c r="Q17" s="28"/>
+      <c r="R17" s="28"/>
+      <c r="S17" s="28"/>
+      <c r="T17" s="28"/>
       <c r="U17" s="21"/>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.6">
-      <c r="C24" s="22" t="s">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.4">
+      <c r="C24" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="I24" s="22" t="s">
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="I24" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
-      <c r="M24" s="22"/>
-      <c r="P24" s="22" t="s">
+      <c r="J24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="27"/>
+      <c r="P24" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="Q24" s="22"/>
-      <c r="R24" s="22"/>
-      <c r="S24" s="22"/>
-      <c r="T24" s="22"/>
+      <c r="Q24" s="27"/>
+      <c r="R24" s="27"/>
+      <c r="S24" s="27"/>
+      <c r="T24" s="27"/>
       <c r="U24" s="21"/>
-      <c r="W24" s="22" t="s">
+      <c r="W24" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="X24" s="22"/>
-      <c r="Y24" s="22"/>
-      <c r="Z24" s="22"/>
-      <c r="AA24" s="22"/>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.6">
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="23"/>
-      <c r="P25" s="23"/>
-      <c r="Q25" s="23"/>
-      <c r="R25" s="23"/>
-      <c r="S25" s="23"/>
-      <c r="T25" s="23"/>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="27"/>
+      <c r="Z24" s="27"/>
+      <c r="AA24" s="27"/>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.4">
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28"/>
+      <c r="P25" s="28"/>
+      <c r="Q25" s="28"/>
+      <c r="R25" s="28"/>
+      <c r="S25" s="28"/>
+      <c r="T25" s="28"/>
       <c r="U25" s="21"/>
-      <c r="W25" s="23"/>
-      <c r="X25" s="23"/>
-      <c r="Y25" s="23"/>
-      <c r="Z25" s="23"/>
-      <c r="AA25" s="23"/>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.6">
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="23"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="23"/>
-      <c r="M26" s="23"/>
-      <c r="P26" s="23"/>
-      <c r="Q26" s="23"/>
-      <c r="R26" s="23"/>
-      <c r="S26" s="23"/>
-      <c r="T26" s="23"/>
+      <c r="W25" s="28"/>
+      <c r="X25" s="28"/>
+      <c r="Y25" s="28"/>
+      <c r="Z25" s="28"/>
+      <c r="AA25" s="28"/>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.4">
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="28"/>
+      <c r="P26" s="28"/>
+      <c r="Q26" s="28"/>
+      <c r="R26" s="28"/>
+      <c r="S26" s="28"/>
+      <c r="T26" s="28"/>
       <c r="U26" s="21"/>
-      <c r="W26" s="23"/>
-      <c r="X26" s="23"/>
-      <c r="Y26" s="23"/>
-      <c r="Z26" s="23"/>
-      <c r="AA26" s="23"/>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.6">
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="23"/>
-      <c r="M27" s="23"/>
-      <c r="P27" s="23"/>
-      <c r="Q27" s="23"/>
-      <c r="R27" s="23"/>
-      <c r="S27" s="23"/>
-      <c r="T27" s="23"/>
+      <c r="W26" s="28"/>
+      <c r="X26" s="28"/>
+      <c r="Y26" s="28"/>
+      <c r="Z26" s="28"/>
+      <c r="AA26" s="28"/>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.4">
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+      <c r="M27" s="28"/>
+      <c r="P27" s="28"/>
+      <c r="Q27" s="28"/>
+      <c r="R27" s="28"/>
+      <c r="S27" s="28"/>
+      <c r="T27" s="28"/>
       <c r="U27" s="21"/>
-      <c r="W27" s="23"/>
-      <c r="X27" s="23"/>
-      <c r="Y27" s="23"/>
-      <c r="Z27" s="23"/>
-      <c r="AA27" s="23"/>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.6">
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="23"/>
-      <c r="R28" s="23"/>
-      <c r="S28" s="23"/>
-      <c r="T28" s="23"/>
+      <c r="W27" s="28"/>
+      <c r="X27" s="28"/>
+      <c r="Y27" s="28"/>
+      <c r="Z27" s="28"/>
+      <c r="AA27" s="28"/>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.4">
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="28"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="28"/>
+      <c r="R28" s="28"/>
+      <c r="S28" s="28"/>
+      <c r="T28" s="28"/>
       <c r="U28" s="21"/>
-      <c r="W28" s="23"/>
-      <c r="X28" s="23"/>
-      <c r="Y28" s="23"/>
-      <c r="Z28" s="23"/>
-      <c r="AA28" s="23"/>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.6">
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="23"/>
-      <c r="L29" s="23"/>
-      <c r="M29" s="23"/>
-      <c r="P29" s="23"/>
-      <c r="Q29" s="23"/>
-      <c r="R29" s="23"/>
-      <c r="S29" s="23"/>
-      <c r="T29" s="23"/>
+      <c r="W28" s="28"/>
+      <c r="X28" s="28"/>
+      <c r="Y28" s="28"/>
+      <c r="Z28" s="28"/>
+      <c r="AA28" s="28"/>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.4">
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+      <c r="M29" s="28"/>
+      <c r="P29" s="28"/>
+      <c r="Q29" s="28"/>
+      <c r="R29" s="28"/>
+      <c r="S29" s="28"/>
+      <c r="T29" s="28"/>
       <c r="U29" s="21"/>
-      <c r="W29" s="23"/>
-      <c r="X29" s="23"/>
-      <c r="Y29" s="23"/>
-      <c r="Z29" s="23"/>
-      <c r="AA29" s="23"/>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.6">
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="23"/>
-      <c r="K30" s="23"/>
-      <c r="L30" s="23"/>
-      <c r="M30" s="23"/>
-      <c r="P30" s="23"/>
-      <c r="Q30" s="23"/>
-      <c r="R30" s="23"/>
-      <c r="S30" s="23"/>
-      <c r="T30" s="23"/>
+      <c r="W29" s="28"/>
+      <c r="X29" s="28"/>
+      <c r="Y29" s="28"/>
+      <c r="Z29" s="28"/>
+      <c r="AA29" s="28"/>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.4">
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="28"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+      <c r="M30" s="28"/>
+      <c r="P30" s="28"/>
+      <c r="Q30" s="28"/>
+      <c r="R30" s="28"/>
+      <c r="S30" s="28"/>
+      <c r="T30" s="28"/>
       <c r="U30" s="21"/>
-      <c r="W30" s="23"/>
-      <c r="X30" s="23"/>
-      <c r="Y30" s="23"/>
-      <c r="Z30" s="23"/>
-      <c r="AA30" s="23"/>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.6">
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="I31" s="23"/>
-      <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
-      <c r="P31" s="23"/>
-      <c r="Q31" s="23"/>
-      <c r="R31" s="23"/>
-      <c r="S31" s="23"/>
-      <c r="T31" s="23"/>
+      <c r="W30" s="28"/>
+      <c r="X30" s="28"/>
+      <c r="Y30" s="28"/>
+      <c r="Z30" s="28"/>
+      <c r="AA30" s="28"/>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.4">
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="I31" s="28"/>
+      <c r="J31" s="28"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+      <c r="M31" s="28"/>
+      <c r="P31" s="28"/>
+      <c r="Q31" s="28"/>
+      <c r="R31" s="28"/>
+      <c r="S31" s="28"/>
+      <c r="T31" s="28"/>
       <c r="U31" s="21"/>
-      <c r="W31" s="23"/>
-      <c r="X31" s="23"/>
-      <c r="Y31" s="23"/>
-      <c r="Z31" s="23"/>
-      <c r="AA31" s="23"/>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.6">
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
-      <c r="I32" s="23"/>
-      <c r="J32" s="23"/>
-      <c r="K32" s="23"/>
-      <c r="L32" s="23"/>
-      <c r="M32" s="23"/>
-      <c r="P32" s="23"/>
-      <c r="Q32" s="23"/>
-      <c r="R32" s="23"/>
-      <c r="S32" s="23"/>
-      <c r="T32" s="23"/>
+      <c r="W31" s="28"/>
+      <c r="X31" s="28"/>
+      <c r="Y31" s="28"/>
+      <c r="Z31" s="28"/>
+      <c r="AA31" s="28"/>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.4">
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
       <c r="U32" s="21"/>
-      <c r="W32" s="23"/>
-      <c r="X32" s="23"/>
-      <c r="Y32" s="23"/>
-      <c r="Z32" s="23"/>
-      <c r="AA32" s="23"/>
-    </row>
-    <row r="33" spans="3:27" x14ac:dyDescent="0.6">
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="23"/>
-      <c r="M33" s="23"/>
-      <c r="P33" s="23"/>
-      <c r="Q33" s="23"/>
-      <c r="R33" s="23"/>
-      <c r="S33" s="23"/>
-      <c r="T33" s="23"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="28"/>
+      <c r="Y32" s="28"/>
+      <c r="Z32" s="28"/>
+      <c r="AA32" s="28"/>
+    </row>
+    <row r="33" spans="3:27" x14ac:dyDescent="0.4">
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+      <c r="M33" s="28"/>
+      <c r="P33" s="28"/>
+      <c r="Q33" s="28"/>
+      <c r="R33" s="28"/>
+      <c r="S33" s="28"/>
+      <c r="T33" s="28"/>
       <c r="U33" s="21"/>
-      <c r="W33" s="23"/>
-      <c r="X33" s="23"/>
-      <c r="Y33" s="23"/>
-      <c r="Z33" s="23"/>
-      <c r="AA33" s="23"/>
-    </row>
-    <row r="34" spans="3:27" x14ac:dyDescent="0.6">
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
-      <c r="I34" s="23"/>
-      <c r="J34" s="23"/>
-      <c r="K34" s="23"/>
-      <c r="L34" s="23"/>
-      <c r="M34" s="23"/>
-      <c r="P34" s="23"/>
-      <c r="Q34" s="23"/>
-      <c r="R34" s="23"/>
-      <c r="S34" s="23"/>
-      <c r="T34" s="23"/>
+      <c r="W33" s="28"/>
+      <c r="X33" s="28"/>
+      <c r="Y33" s="28"/>
+      <c r="Z33" s="28"/>
+      <c r="AA33" s="28"/>
+    </row>
+    <row r="34" spans="3:27" x14ac:dyDescent="0.4">
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="28"/>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="28"/>
+      <c r="R34" s="28"/>
+      <c r="S34" s="28"/>
+      <c r="T34" s="28"/>
       <c r="U34" s="21"/>
-      <c r="W34" s="23"/>
-      <c r="X34" s="23"/>
-      <c r="Y34" s="23"/>
-      <c r="Z34" s="23"/>
-      <c r="AA34" s="23"/>
-    </row>
-    <row r="35" spans="3:27" x14ac:dyDescent="0.6">
-      <c r="I35" s="23"/>
-      <c r="J35" s="23"/>
-      <c r="K35" s="23"/>
-      <c r="L35" s="23"/>
-      <c r="M35" s="23"/>
-      <c r="P35" s="23"/>
-      <c r="Q35" s="23"/>
-      <c r="R35" s="23"/>
-      <c r="S35" s="23"/>
-      <c r="T35" s="23"/>
+      <c r="W34" s="28"/>
+      <c r="X34" s="28"/>
+      <c r="Y34" s="28"/>
+      <c r="Z34" s="28"/>
+      <c r="AA34" s="28"/>
+    </row>
+    <row r="35" spans="3:27" x14ac:dyDescent="0.4">
+      <c r="I35" s="28"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+      <c r="M35" s="28"/>
+      <c r="P35" s="28"/>
+      <c r="Q35" s="28"/>
+      <c r="R35" s="28"/>
+      <c r="S35" s="28"/>
+      <c r="T35" s="28"/>
       <c r="U35" s="21"/>
-      <c r="W35" s="23"/>
-      <c r="X35" s="23"/>
-      <c r="Y35" s="23"/>
-      <c r="Z35" s="23"/>
-      <c r="AA35" s="23"/>
+      <c r="W35" s="28"/>
+      <c r="X35" s="28"/>
+      <c r="Y35" s="28"/>
+      <c r="Z35" s="28"/>
+      <c r="AA35" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -7987,49 +9260,49 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60644CBA-8A35-B448-A8AD-7C90B5DB5344}">
   <dimension ref="A1:S46"/>
-  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="20" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="11.109375" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="4" width="3.15234375" customWidth="1"/>
+    <col min="1" max="4" width="3.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.6">
-      <c r="B6" s="24" t="s">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="B6" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25"/>
-      <c r="P6" s="25"/>
-      <c r="Q6" s="25"/>
-      <c r="R6" s="25"/>
-      <c r="S6" s="26"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.6">
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="30"/>
+      <c r="R6" s="30"/>
+      <c r="S6" s="31"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B7" s="2"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -8049,29 +9322,29 @@
       <c r="R7" s="3"/>
       <c r="S7" s="4"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B8" s="5"/>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="27"/>
-      <c r="O8" s="27"/>
-      <c r="P8" s="27"/>
-      <c r="Q8" s="27"/>
-      <c r="R8" s="27"/>
-      <c r="S8" s="27"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.6">
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="32"/>
+      <c r="R8" s="32"/>
+      <c r="S8" s="32"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B9" s="5"/>
       <c r="C9" s="2"/>
       <c r="D9" s="3"/>
@@ -8091,35 +9364,35 @@
       <c r="R9" s="3"/>
       <c r="S9" s="4"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="27"/>
-      <c r="L10" s="27"/>
-      <c r="M10" s="27"/>
-      <c r="N10" s="27"/>
-      <c r="O10" s="27"/>
-      <c r="P10" s="27"/>
-      <c r="Q10" s="27"/>
-      <c r="R10" s="27"/>
-      <c r="S10" s="27"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.6">
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="32"/>
+      <c r="Q10" s="32"/>
+      <c r="R10" s="32"/>
+      <c r="S10" s="32"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="S11" s="6"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -8128,235 +9401,235 @@
       </c>
       <c r="S12" s="6"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="S13" s="6"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="J14" s="22" t="s">
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="J14" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="O14" s="22" t="s">
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="O14" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="22"/>
-      <c r="R14" s="22"/>
+      <c r="P14" s="27"/>
+      <c r="Q14" s="27"/>
+      <c r="R14" s="27"/>
       <c r="S14" s="6"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="28"/>
+      <c r="R15" s="28"/>
       <c r="S15" s="6"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
       <c r="S16" s="6"/>
     </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="17" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="28"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="28"/>
+      <c r="Q17" s="28"/>
+      <c r="R17" s="28"/>
       <c r="S17" s="6"/>
     </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="18" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="28"/>
+      <c r="O18" s="28"/>
+      <c r="P18" s="28"/>
+      <c r="Q18" s="28"/>
+      <c r="R18" s="28"/>
       <c r="S18" s="6"/>
     </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="19" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
-      <c r="J19" s="23"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="28"/>
+      <c r="Q19" s="28"/>
+      <c r="R19" s="28"/>
       <c r="S19" s="6"/>
     </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="20" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="28"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="28"/>
+      <c r="Q20" s="28"/>
+      <c r="R20" s="28"/>
       <c r="S20" s="6"/>
     </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="21" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="28"/>
+      <c r="O21" s="28"/>
+      <c r="P21" s="28"/>
+      <c r="Q21" s="28"/>
+      <c r="R21" s="28"/>
       <c r="S21" s="6"/>
     </row>
-    <row r="22" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="22" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="28"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="28"/>
+      <c r="Q22" s="28"/>
+      <c r="R22" s="28"/>
       <c r="S22" s="6"/>
     </row>
-    <row r="23" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="23" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
-      <c r="O23" s="23"/>
-      <c r="P23" s="23"/>
-      <c r="Q23" s="23"/>
-      <c r="R23" s="23"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
+      <c r="O23" s="28"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="28"/>
+      <c r="R23" s="28"/>
       <c r="S23" s="6"/>
     </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="24" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="23"/>
-      <c r="O24" s="23"/>
-      <c r="P24" s="23"/>
-      <c r="Q24" s="23"/>
-      <c r="R24" s="23"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="28"/>
+      <c r="O24" s="28"/>
+      <c r="P24" s="28"/>
+      <c r="Q24" s="28"/>
+      <c r="R24" s="28"/>
       <c r="S24" s="6"/>
     </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="25" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="23"/>
-      <c r="O25" s="23"/>
-      <c r="P25" s="23"/>
-      <c r="Q25" s="23"/>
-      <c r="R25" s="23"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="28"/>
+      <c r="Q25" s="28"/>
+      <c r="R25" s="28"/>
       <c r="S25" s="6"/>
     </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="26" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
       <c r="D26" s="10"/>
@@ -8376,40 +9649,40 @@
       <c r="R26" s="11"/>
       <c r="S26" s="12"/>
     </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="27" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="S27" s="6"/>
     </row>
-    <row r="28" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="28" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="27" t="s">
+      <c r="D28" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="27"/>
-      <c r="K28" s="27"/>
-      <c r="L28" s="27"/>
-      <c r="M28" s="27"/>
-      <c r="N28" s="27"/>
-      <c r="O28" s="27"/>
-      <c r="P28" s="27"/>
-      <c r="Q28" s="27"/>
-      <c r="R28" s="27"/>
-      <c r="S28" s="27"/>
-    </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.6">
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+    </row>
+    <row r="29" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="S29" s="6"/>
     </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="30" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -8418,235 +9691,235 @@
       </c>
       <c r="S30" s="6"/>
     </row>
-    <row r="31" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="31" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="S31" s="6"/>
     </row>
-    <row r="32" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="32" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
-      <c r="E32" s="22" t="s">
+      <c r="E32" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="J32" s="22" t="s">
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="J32" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
-      <c r="M32" s="22"/>
-      <c r="O32" s="22" t="s">
+      <c r="K32" s="27"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="27"/>
+      <c r="O32" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="P32" s="22"/>
-      <c r="Q32" s="22"/>
-      <c r="R32" s="22"/>
+      <c r="P32" s="27"/>
+      <c r="Q32" s="27"/>
+      <c r="R32" s="27"/>
       <c r="S32" s="6"/>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="23"/>
-      <c r="M33" s="23"/>
-      <c r="O33" s="23"/>
-      <c r="P33" s="23"/>
-      <c r="Q33" s="23"/>
-      <c r="R33" s="23"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="J33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+      <c r="M33" s="28"/>
+      <c r="O33" s="28"/>
+      <c r="P33" s="28"/>
+      <c r="Q33" s="28"/>
+      <c r="R33" s="28"/>
       <c r="S33" s="6"/>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="23"/>
-      <c r="J34" s="23"/>
-      <c r="K34" s="23"/>
-      <c r="L34" s="23"/>
-      <c r="M34" s="23"/>
-      <c r="O34" s="23"/>
-      <c r="P34" s="23"/>
-      <c r="Q34" s="23"/>
-      <c r="R34" s="23"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="J34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="28"/>
+      <c r="O34" s="28"/>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="28"/>
+      <c r="R34" s="28"/>
       <c r="S34" s="6"/>
     </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="35" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="23"/>
-      <c r="J35" s="23"/>
-      <c r="K35" s="23"/>
-      <c r="L35" s="23"/>
-      <c r="M35" s="23"/>
-      <c r="O35" s="23"/>
-      <c r="P35" s="23"/>
-      <c r="Q35" s="23"/>
-      <c r="R35" s="23"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+      <c r="M35" s="28"/>
+      <c r="O35" s="28"/>
+      <c r="P35" s="28"/>
+      <c r="Q35" s="28"/>
+      <c r="R35" s="28"/>
       <c r="S35" s="6"/>
     </row>
-    <row r="36" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="36" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="23"/>
-      <c r="J36" s="23"/>
-      <c r="K36" s="23"/>
-      <c r="L36" s="23"/>
-      <c r="M36" s="23"/>
-      <c r="O36" s="23"/>
-      <c r="P36" s="23"/>
-      <c r="Q36" s="23"/>
-      <c r="R36" s="23"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="28"/>
+      <c r="O36" s="28"/>
+      <c r="P36" s="28"/>
+      <c r="Q36" s="28"/>
+      <c r="R36" s="28"/>
       <c r="S36" s="6"/>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="23"/>
-      <c r="J37" s="23"/>
-      <c r="K37" s="23"/>
-      <c r="L37" s="23"/>
-      <c r="M37" s="23"/>
-      <c r="O37" s="23"/>
-      <c r="P37" s="23"/>
-      <c r="Q37" s="23"/>
-      <c r="R37" s="23"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
       <c r="S37" s="6"/>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="23"/>
-      <c r="J38" s="23"/>
-      <c r="K38" s="23"/>
-      <c r="L38" s="23"/>
-      <c r="M38" s="23"/>
-      <c r="O38" s="23"/>
-      <c r="P38" s="23"/>
-      <c r="Q38" s="23"/>
-      <c r="R38" s="23"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+      <c r="J38" s="28"/>
+      <c r="K38" s="28"/>
+      <c r="L38" s="28"/>
+      <c r="M38" s="28"/>
+      <c r="O38" s="28"/>
+      <c r="P38" s="28"/>
+      <c r="Q38" s="28"/>
+      <c r="R38" s="28"/>
       <c r="S38" s="6"/>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="23"/>
-      <c r="H39" s="23"/>
-      <c r="J39" s="23"/>
-      <c r="K39" s="23"/>
-      <c r="L39" s="23"/>
-      <c r="M39" s="23"/>
-      <c r="O39" s="23"/>
-      <c r="P39" s="23"/>
-      <c r="Q39" s="23"/>
-      <c r="R39" s="23"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="28"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="28"/>
+      <c r="O39" s="28"/>
+      <c r="P39" s="28"/>
+      <c r="Q39" s="28"/>
+      <c r="R39" s="28"/>
       <c r="S39" s="6"/>
     </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="40" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="J40" s="23"/>
-      <c r="K40" s="23"/>
-      <c r="L40" s="23"/>
-      <c r="M40" s="23"/>
-      <c r="O40" s="23"/>
-      <c r="P40" s="23"/>
-      <c r="Q40" s="23"/>
-      <c r="R40" s="23"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
+      <c r="O40" s="28"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="28"/>
+      <c r="R40" s="28"/>
       <c r="S40" s="6"/>
     </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="41" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="23"/>
-      <c r="J41" s="23"/>
-      <c r="K41" s="23"/>
-      <c r="L41" s="23"/>
-      <c r="M41" s="23"/>
-      <c r="O41" s="23"/>
-      <c r="P41" s="23"/>
-      <c r="Q41" s="23"/>
-      <c r="R41" s="23"/>
+      <c r="E41" s="28"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="28"/>
+      <c r="J41" s="28"/>
+      <c r="K41" s="28"/>
+      <c r="L41" s="28"/>
+      <c r="M41" s="28"/>
+      <c r="O41" s="28"/>
+      <c r="P41" s="28"/>
+      <c r="Q41" s="28"/>
+      <c r="R41" s="28"/>
       <c r="S41" s="6"/>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="23"/>
-      <c r="J42" s="23"/>
-      <c r="K42" s="23"/>
-      <c r="L42" s="23"/>
-      <c r="M42" s="23"/>
-      <c r="O42" s="23"/>
-      <c r="P42" s="23"/>
-      <c r="Q42" s="23"/>
-      <c r="R42" s="23"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
+      <c r="J42" s="28"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="28"/>
+      <c r="M42" s="28"/>
+      <c r="O42" s="28"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="28"/>
+      <c r="R42" s="28"/>
       <c r="S42" s="6"/>
     </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="43" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="23"/>
-      <c r="H43" s="23"/>
-      <c r="J43" s="23"/>
-      <c r="K43" s="23"/>
-      <c r="L43" s="23"/>
-      <c r="M43" s="23"/>
-      <c r="O43" s="23"/>
-      <c r="P43" s="23"/>
-      <c r="Q43" s="23"/>
-      <c r="R43" s="23"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="28"/>
+      <c r="O43" s="28"/>
+      <c r="P43" s="28"/>
+      <c r="Q43" s="28"/>
+      <c r="R43" s="28"/>
       <c r="S43" s="6"/>
     </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
       <c r="D44" s="10"/>
@@ -8666,7 +9939,7 @@
       <c r="R44" s="11"/>
       <c r="S44" s="12"/>
     </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B45" s="5"/>
       <c r="C45" s="10"/>
       <c r="D45" s="11"/>
@@ -8686,7 +9959,7 @@
       <c r="R45" s="11"/>
       <c r="S45" s="12"/>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B46" s="7"/>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
@@ -8735,39 +10008,39 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EF1127F-C553-8844-9E64-B7B91034C69E}">
   <dimension ref="A1:W100"/>
-  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="20" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="11.109375" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>79</v>
       </c>
@@ -8775,112 +10048,112 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A10" s="13"/>
       <c r="B10" s="13" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A11" s="13"/>
       <c r="B11" s="13" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.6"/>
-    <row r="13" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="22" t="s">
+    <row r="12" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="13" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="22"/>
-      <c r="D13" s="22" t="s">
+      <c r="B13" s="27"/>
+      <c r="D13" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
-      <c r="O13" s="35" t="s">
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="O13" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="P13" s="37"/>
-      <c r="R13" s="32" t="s">
+      <c r="P13" s="42"/>
+      <c r="R13" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="S13" s="33"/>
-      <c r="T13" s="33"/>
-      <c r="U13" s="33"/>
-      <c r="V13" s="33"/>
-      <c r="W13" s="29"/>
-    </row>
-    <row r="14" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="D14" s="22" t="s">
+      <c r="S13" s="38"/>
+      <c r="T13" s="38"/>
+      <c r="U13" s="38"/>
+      <c r="V13" s="38"/>
+      <c r="W13" s="34"/>
+    </row>
+    <row r="14" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="27"/>
+      <c r="B14" s="27"/>
+      <c r="D14" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="35"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="36"/>
-      <c r="L14" s="36"/>
-      <c r="M14" s="37"/>
-      <c r="O14" s="28" t="s">
+      <c r="E14" s="40"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="41"/>
+      <c r="L14" s="41"/>
+      <c r="M14" s="42"/>
+      <c r="O14" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="P14" s="29"/>
-      <c r="R14" s="30"/>
-      <c r="S14" s="34"/>
-      <c r="T14" s="34"/>
-      <c r="U14" s="34"/>
-      <c r="V14" s="34"/>
-      <c r="W14" s="31"/>
-    </row>
-    <row r="15" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="22"/>
-      <c r="B15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22" t="s">
+      <c r="P14" s="34"/>
+      <c r="R14" s="35"/>
+      <c r="S14" s="39"/>
+      <c r="T14" s="39"/>
+      <c r="U14" s="39"/>
+      <c r="V14" s="39"/>
+      <c r="W14" s="36"/>
+    </row>
+    <row r="15" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="27"/>
+      <c r="B15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22" t="s">
+      <c r="G15" s="27"/>
+      <c r="H15" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22" t="s">
+      <c r="I15" s="27"/>
+      <c r="J15" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22" t="s">
+      <c r="K15" s="27"/>
+      <c r="L15" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="M15" s="22"/>
-      <c r="O15" s="30"/>
-      <c r="P15" s="31"/>
-      <c r="R15" s="22" t="s">
+      <c r="M15" s="27"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="36"/>
+      <c r="R15" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="S15" s="22"/>
-      <c r="T15" s="22" t="s">
+      <c r="S15" s="27"/>
+      <c r="T15" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="U15" s="22"/>
-      <c r="V15" s="22" t="s">
+      <c r="U15" s="27"/>
+      <c r="V15" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="W15" s="22"/>
-    </row>
-    <row r="16" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="W15" s="27"/>
+    </row>
+    <row r="16" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="5"/>
       <c r="E16" s="5"/>
       <c r="G16" s="5"/>
@@ -8892,7 +10165,7 @@
       <c r="U16" s="5"/>
       <c r="W16" s="5"/>
     </row>
-    <row r="17" spans="2:23" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="17" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="5"/>
       <c r="E17" s="5"/>
       <c r="G17" s="5"/>
@@ -8907,7 +10180,7 @@
       <c r="U17" s="5"/>
       <c r="W17" s="5"/>
     </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="18" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B18" s="5"/>
       <c r="E18" s="5"/>
       <c r="G18" s="5"/>
@@ -8919,7 +10192,7 @@
       <c r="U18" s="5"/>
       <c r="W18" s="5"/>
     </row>
-    <row r="19" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="19" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B19" s="5"/>
       <c r="E19" s="5"/>
       <c r="G19" s="5"/>
@@ -8931,7 +10204,7 @@
       <c r="U19" s="5"/>
       <c r="W19" s="5"/>
     </row>
-    <row r="20" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="20" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B20" s="5"/>
       <c r="E20" s="15" t="s">
         <v>43</v>
@@ -8948,7 +10221,7 @@
       <c r="U20" s="5"/>
       <c r="W20" s="5"/>
     </row>
-    <row r="21" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="21" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B21" s="5"/>
       <c r="E21" s="5"/>
       <c r="G21" s="5"/>
@@ -8960,7 +10233,7 @@
       <c r="U21" s="5"/>
       <c r="W21" s="5"/>
     </row>
-    <row r="22" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="22" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B22" s="5"/>
       <c r="E22" s="5"/>
       <c r="G22" s="5"/>
@@ -8975,7 +10248,7 @@
       <c r="U22" s="5"/>
       <c r="W22" s="5"/>
     </row>
-    <row r="23" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="23" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B23" s="5"/>
       <c r="E23" s="5"/>
       <c r="G23" s="5"/>
@@ -8990,7 +10263,7 @@
       <c r="U23" s="5"/>
       <c r="W23" s="5"/>
     </row>
-    <row r="24" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="24" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B24" s="5"/>
       <c r="E24" s="5"/>
       <c r="G24" s="5"/>
@@ -9002,7 +10275,7 @@
       <c r="U24" s="5"/>
       <c r="W24" s="5"/>
     </row>
-    <row r="25" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="25" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B25" s="5"/>
       <c r="E25" s="5"/>
       <c r="G25" s="5"/>
@@ -9017,7 +10290,7 @@
       <c r="U25" s="5"/>
       <c r="W25" s="5"/>
     </row>
-    <row r="26" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="26" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B26" s="5"/>
       <c r="E26" s="5"/>
       <c r="G26" s="5"/>
@@ -9032,7 +10305,7 @@
       <c r="U26" s="5"/>
       <c r="W26" s="5"/>
     </row>
-    <row r="27" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="27" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B27" s="5"/>
       <c r="E27" s="5"/>
       <c r="G27" s="5"/>
@@ -9044,7 +10317,7 @@
       <c r="U27" s="5"/>
       <c r="W27" s="5"/>
     </row>
-    <row r="28" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="28" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B28" s="5"/>
       <c r="E28" s="5"/>
       <c r="G28" s="5"/>
@@ -9056,7 +10329,7 @@
       <c r="U28" s="5"/>
       <c r="W28" s="5"/>
     </row>
-    <row r="29" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="29" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B29" s="5"/>
       <c r="E29" s="5"/>
       <c r="F29" s="14" t="s">
@@ -9071,7 +10344,7 @@
       <c r="U29" s="5"/>
       <c r="W29" s="5"/>
     </row>
-    <row r="30" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="30" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B30" s="5"/>
       <c r="E30" s="5"/>
       <c r="G30" s="5"/>
@@ -9083,7 +10356,7 @@
       <c r="U30" s="5"/>
       <c r="W30" s="5"/>
     </row>
-    <row r="31" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="31" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B31" s="5"/>
       <c r="E31" s="5"/>
       <c r="G31" s="5"/>
@@ -9098,7 +10371,7 @@
       <c r="U31" s="5"/>
       <c r="W31" s="5"/>
     </row>
-    <row r="32" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="32" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B32" s="5"/>
       <c r="E32" s="5"/>
       <c r="G32" s="5"/>
@@ -9110,7 +10383,7 @@
       <c r="U32" s="5"/>
       <c r="W32" s="5"/>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B33" s="5"/>
       <c r="E33" s="5"/>
       <c r="G33" s="5"/>
@@ -9125,7 +10398,7 @@
       <c r="U33" s="5"/>
       <c r="W33" s="5"/>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B34" s="5"/>
       <c r="E34" s="5"/>
       <c r="G34" s="5"/>
@@ -9137,7 +10410,7 @@
       <c r="U34" s="5"/>
       <c r="W34" s="5"/>
     </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="35" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B35" s="5"/>
       <c r="E35" s="5"/>
       <c r="G35" s="5"/>
@@ -9149,7 +10422,7 @@
       <c r="U35" s="5"/>
       <c r="W35" s="5"/>
     </row>
-    <row r="36" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="36" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B36" s="5"/>
       <c r="E36" s="5"/>
       <c r="F36" s="14" t="s">
@@ -9164,7 +10437,7 @@
       <c r="U36" s="5"/>
       <c r="W36" s="5"/>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B37" s="5"/>
       <c r="E37" s="5"/>
       <c r="G37" s="5"/>
@@ -9176,7 +10449,7 @@
       <c r="U37" s="5"/>
       <c r="W37" s="5"/>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B38" s="5"/>
       <c r="E38" s="5"/>
       <c r="G38" s="5"/>
@@ -9188,7 +10461,7 @@
       <c r="U38" s="5"/>
       <c r="W38" s="5"/>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B39" s="5"/>
       <c r="E39" s="15" t="s">
         <v>49</v>
@@ -9202,7 +10475,7 @@
       <c r="U39" s="5"/>
       <c r="W39" s="5"/>
     </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="40" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B40" s="5"/>
       <c r="E40" s="5"/>
       <c r="G40" s="5"/>
@@ -9214,7 +10487,7 @@
       <c r="U40" s="5"/>
       <c r="W40" s="5"/>
     </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="41" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B41" s="5"/>
       <c r="E41" s="15" t="s">
         <v>54</v>
@@ -9231,7 +10504,7 @@
       <c r="U41" s="5"/>
       <c r="W41" s="5"/>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B42" s="5"/>
       <c r="E42" s="15" t="s">
         <v>55</v>
@@ -9248,7 +10521,7 @@
       <c r="U42" s="5"/>
       <c r="W42" s="5"/>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="43" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B43" s="5"/>
       <c r="E43" s="5"/>
       <c r="G43" s="5"/>
@@ -9260,7 +10533,7 @@
       <c r="U43" s="5"/>
       <c r="W43" s="5"/>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B44" s="5"/>
       <c r="E44" s="5"/>
       <c r="G44" s="5"/>
@@ -9272,7 +10545,7 @@
       <c r="U44" s="5"/>
       <c r="W44" s="5"/>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B45" s="5"/>
       <c r="E45" s="5"/>
       <c r="G45" s="5"/>
@@ -9287,7 +10560,7 @@
       <c r="U45" s="5"/>
       <c r="W45" s="5"/>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B46" s="5"/>
       <c r="E46" s="5"/>
       <c r="G46" s="5"/>
@@ -9299,7 +10572,7 @@
       <c r="U46" s="5"/>
       <c r="W46" s="5"/>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B47" s="5"/>
       <c r="E47" s="5"/>
       <c r="G47" s="5"/>
@@ -9311,7 +10584,7 @@
       <c r="U47" s="5"/>
       <c r="W47" s="5"/>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B48" s="5"/>
       <c r="E48" s="15" t="s">
         <v>49</v>
@@ -9325,7 +10598,7 @@
       <c r="U48" s="5"/>
       <c r="W48" s="5"/>
     </row>
-    <row r="49" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="49" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B49" s="5"/>
       <c r="E49" s="5"/>
       <c r="G49" s="5"/>
@@ -9337,7 +10610,7 @@
       <c r="U49" s="5"/>
       <c r="W49" s="5"/>
     </row>
-    <row r="50" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="50" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B50" s="5"/>
       <c r="E50" s="5"/>
       <c r="G50" s="5"/>
@@ -9349,7 +10622,7 @@
       <c r="U50" s="5"/>
       <c r="W50" s="5"/>
     </row>
-    <row r="51" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="51" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B51" s="5"/>
       <c r="E51" s="15" t="s">
         <v>54</v>
@@ -9366,7 +10639,7 @@
       <c r="U51" s="5"/>
       <c r="W51" s="5"/>
     </row>
-    <row r="52" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="52" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B52" s="5"/>
       <c r="E52" s="15" t="s">
         <v>55</v>
@@ -9383,7 +10656,7 @@
       <c r="U52" s="5"/>
       <c r="W52" s="5"/>
     </row>
-    <row r="53" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="53" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B53" s="5"/>
       <c r="E53" s="5"/>
       <c r="G53" s="5"/>
@@ -9395,7 +10668,7 @@
       <c r="U53" s="5"/>
       <c r="W53" s="5"/>
     </row>
-    <row r="54" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="54" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B54" s="5"/>
       <c r="E54" s="5"/>
       <c r="G54" s="5"/>
@@ -9407,7 +10680,7 @@
       <c r="U54" s="5"/>
       <c r="W54" s="5"/>
     </row>
-    <row r="55" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="55" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B55" s="5"/>
       <c r="E55" s="5"/>
       <c r="G55" s="5"/>
@@ -9422,7 +10695,7 @@
       <c r="U55" s="5"/>
       <c r="W55" s="5"/>
     </row>
-    <row r="56" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="56" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B56" s="5"/>
       <c r="E56" s="5"/>
       <c r="G56" s="5"/>
@@ -9434,7 +10707,7 @@
       <c r="U56" s="5"/>
       <c r="W56" s="5"/>
     </row>
-    <row r="57" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="57" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B57" s="5"/>
       <c r="E57" s="15" t="s">
         <v>2</v>
@@ -9448,7 +10721,7 @@
       <c r="U57" s="5"/>
       <c r="W57" s="5"/>
     </row>
-    <row r="58" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="58" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B58" s="5"/>
       <c r="E58" s="15" t="s">
         <v>58</v>
@@ -9462,7 +10735,7 @@
       <c r="U58" s="5"/>
       <c r="W58" s="5"/>
     </row>
-    <row r="59" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="59" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B59" s="5"/>
       <c r="E59" s="5"/>
       <c r="G59" s="5"/>
@@ -9474,7 +10747,7 @@
       <c r="U59" s="5"/>
       <c r="W59" s="5"/>
     </row>
-    <row r="60" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="60" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B60" s="5"/>
       <c r="E60" s="5"/>
       <c r="G60" s="5"/>
@@ -9486,7 +10759,7 @@
       <c r="U60" s="5"/>
       <c r="W60" s="5"/>
     </row>
-    <row r="61" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="61" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B61" s="5"/>
       <c r="E61" s="5"/>
       <c r="G61" s="5"/>
@@ -9501,7 +10774,7 @@
       <c r="U61" s="5"/>
       <c r="W61" s="5"/>
     </row>
-    <row r="62" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="62" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B62" s="5"/>
       <c r="E62" s="5"/>
       <c r="G62" s="5"/>
@@ -9513,7 +10786,7 @@
       <c r="U62" s="5"/>
       <c r="W62" s="5"/>
     </row>
-    <row r="63" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="63" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B63" s="5"/>
       <c r="E63" s="5"/>
       <c r="G63" s="5"/>
@@ -9525,7 +10798,7 @@
       <c r="U63" s="5"/>
       <c r="W63" s="5"/>
     </row>
-    <row r="64" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="64" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B64" s="5"/>
       <c r="E64" s="5"/>
       <c r="G64" s="5"/>
@@ -9540,7 +10813,7 @@
       <c r="U64" s="5"/>
       <c r="W64" s="5"/>
     </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="65" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B65" s="5"/>
       <c r="E65" s="5"/>
       <c r="G65" s="5"/>
@@ -9552,7 +10825,7 @@
       <c r="U65" s="5"/>
       <c r="W65" s="5"/>
     </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="66" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B66" s="5"/>
       <c r="E66" s="5"/>
       <c r="G66" s="5"/>
@@ -9564,7 +10837,7 @@
       <c r="U66" s="5"/>
       <c r="W66" s="5"/>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B67" s="5"/>
       <c r="E67" s="5"/>
       <c r="G67" s="5"/>
@@ -9578,7 +10851,7 @@
       <c r="U67" s="5"/>
       <c r="W67" s="5"/>
     </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="68" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B68" s="5"/>
       <c r="E68" s="5"/>
       <c r="G68" s="5"/>
@@ -9590,7 +10863,7 @@
       <c r="U68" s="5"/>
       <c r="W68" s="5"/>
     </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="69" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B69" s="5"/>
       <c r="E69" s="15" t="s">
         <v>65</v>
@@ -9604,7 +10877,7 @@
       <c r="U69" s="5"/>
       <c r="W69" s="5"/>
     </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="70" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B70" s="5"/>
       <c r="E70" s="17" t="s">
         <v>66</v>
@@ -9618,7 +10891,7 @@
       <c r="U70" s="5"/>
       <c r="W70" s="5"/>
     </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="71" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B71" s="5"/>
       <c r="E71" s="5"/>
       <c r="G71" s="5"/>
@@ -9630,7 +10903,7 @@
       <c r="U71" s="5"/>
       <c r="W71" s="5"/>
     </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="72" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B72" s="5"/>
       <c r="E72" s="5"/>
       <c r="G72" s="5"/>
@@ -9642,7 +10915,7 @@
       <c r="U72" s="5"/>
       <c r="W72" s="5"/>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B73" s="5"/>
       <c r="E73" s="5"/>
       <c r="G73" s="5"/>
@@ -9657,7 +10930,7 @@
       <c r="U73" s="5"/>
       <c r="W73" s="5"/>
     </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="74" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B74" s="5"/>
       <c r="E74" s="5"/>
       <c r="G74" s="5"/>
@@ -9672,7 +10945,7 @@
       <c r="U74" s="5"/>
       <c r="W74" s="5"/>
     </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="75" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B75" s="5"/>
       <c r="E75" s="5"/>
       <c r="G75" s="5"/>
@@ -9684,7 +10957,7 @@
       <c r="U75" s="5"/>
       <c r="W75" s="5"/>
     </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="76" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B76" s="5"/>
       <c r="E76" s="5"/>
       <c r="G76" s="5"/>
@@ -9699,7 +10972,7 @@
       <c r="U76" s="5"/>
       <c r="W76" s="5"/>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B77" s="5"/>
       <c r="E77" s="5"/>
       <c r="G77" s="5"/>
@@ -9714,7 +10987,7 @@
       <c r="U77" s="5"/>
       <c r="W77" s="5"/>
     </row>
-    <row r="78" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="78" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B78" s="5"/>
       <c r="E78" s="5"/>
       <c r="G78" s="5"/>
@@ -9726,7 +10999,7 @@
       <c r="U78" s="5"/>
       <c r="W78" s="5"/>
     </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="79" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B79" s="5"/>
       <c r="E79" s="5"/>
       <c r="G79" s="5"/>
@@ -9741,7 +11014,7 @@
       </c>
       <c r="W79" s="5"/>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B80" s="5"/>
       <c r="E80" s="5"/>
       <c r="G80" s="5"/>
@@ -9756,7 +11029,7 @@
       </c>
       <c r="W80" s="5"/>
     </row>
-    <row r="81" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="81" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B81" s="5"/>
       <c r="E81" s="5"/>
       <c r="G81" s="5"/>
@@ -9768,7 +11041,7 @@
       <c r="U81" s="5"/>
       <c r="W81" s="5"/>
     </row>
-    <row r="82" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="82" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B82" s="5"/>
       <c r="E82" s="5"/>
       <c r="G82" s="5"/>
@@ -9780,7 +11053,7 @@
       <c r="U82" s="5"/>
       <c r="W82" s="5"/>
     </row>
-    <row r="83" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="83" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B83" s="5"/>
       <c r="E83" s="5"/>
       <c r="G83" s="5"/>
@@ -9795,7 +11068,7 @@
       </c>
       <c r="W83" s="5"/>
     </row>
-    <row r="84" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="84" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B84" s="5"/>
       <c r="E84" s="5"/>
       <c r="G84" s="5"/>
@@ -9808,7 +11081,7 @@
       <c r="V84" s="16"/>
       <c r="W84" s="5"/>
     </row>
-    <row r="85" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="85" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B85" s="5"/>
       <c r="E85" s="5"/>
       <c r="G85" s="5"/>
@@ -9823,7 +11096,7 @@
       <c r="U85" s="5"/>
       <c r="W85" s="5"/>
     </row>
-    <row r="86" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="86" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B86" s="5"/>
       <c r="E86" s="5"/>
       <c r="G86" s="5"/>
@@ -9838,7 +11111,7 @@
       <c r="U86" s="5"/>
       <c r="W86" s="5"/>
     </row>
-    <row r="87" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="87" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B87" s="5"/>
       <c r="E87" s="5"/>
       <c r="G87" s="5"/>
@@ -9850,7 +11123,7 @@
       <c r="U87" s="5"/>
       <c r="W87" s="5"/>
     </row>
-    <row r="88" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="88" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B88" s="5"/>
       <c r="E88" s="5"/>
       <c r="G88" s="5"/>
@@ -9864,7 +11137,7 @@
       <c r="U88" s="5"/>
       <c r="W88" s="5"/>
     </row>
-    <row r="89" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="89" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B89" s="5"/>
       <c r="E89" s="5"/>
       <c r="G89" s="5"/>
@@ -9876,7 +11149,7 @@
       <c r="U89" s="5"/>
       <c r="W89" s="5"/>
     </row>
-    <row r="90" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="90" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B90" s="5"/>
       <c r="E90" s="15" t="s">
         <v>65</v>
@@ -9890,7 +11163,7 @@
       <c r="U90" s="5"/>
       <c r="W90" s="5"/>
     </row>
-    <row r="91" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="91" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B91" s="5"/>
       <c r="E91" s="17" t="s">
         <v>71</v>
@@ -9904,7 +11177,7 @@
       <c r="U91" s="5"/>
       <c r="W91" s="5"/>
     </row>
-    <row r="92" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="92" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B92" s="5"/>
       <c r="E92" s="5"/>
       <c r="G92" s="5"/>
@@ -9916,7 +11189,7 @@
       <c r="U92" s="5"/>
       <c r="W92" s="5"/>
     </row>
-    <row r="93" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="93" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B93" s="5"/>
       <c r="E93" s="5"/>
       <c r="G93" s="5"/>
@@ -9928,7 +11201,7 @@
       <c r="U93" s="5"/>
       <c r="W93" s="5"/>
     </row>
-    <row r="94" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="94" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B94" s="5"/>
       <c r="E94" s="5"/>
       <c r="G94" s="5"/>
@@ -9943,7 +11216,7 @@
       <c r="U94" s="5"/>
       <c r="W94" s="5"/>
     </row>
-    <row r="95" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="95" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B95" s="5"/>
       <c r="E95" s="5"/>
       <c r="G95" s="5"/>
@@ -9958,7 +11231,7 @@
       <c r="U95" s="5"/>
       <c r="W95" s="5"/>
     </row>
-    <row r="96" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="96" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B96" s="5"/>
       <c r="E96" s="5"/>
       <c r="G96" s="5"/>
@@ -9970,7 +11243,7 @@
       <c r="U96" s="5"/>
       <c r="W96" s="5"/>
     </row>
-    <row r="97" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="97" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B97" s="5"/>
       <c r="E97" s="5"/>
       <c r="G97" s="5"/>
@@ -9982,7 +11255,7 @@
       <c r="U97" s="5"/>
       <c r="W97" s="5"/>
     </row>
-    <row r="98" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="98" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B98" s="5"/>
       <c r="E98" s="5"/>
       <c r="G98" s="5"/>
@@ -9994,7 +11267,7 @@
       <c r="U98" s="5"/>
       <c r="W98" s="5"/>
     </row>
-    <row r="99" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="99" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B99" s="5"/>
       <c r="E99" s="18" t="s">
         <v>74</v>
@@ -10008,7 +11281,7 @@
       <c r="U99" s="5"/>
       <c r="W99" s="5"/>
     </row>
-    <row r="100" spans="2:23" x14ac:dyDescent="0.6">
+    <row r="100" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B100" s="5"/>
       <c r="E100" s="18" t="s">
         <v>75</v>
@@ -10047,52 +11320,881 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7A6E992-2845-477B-B54A-912AB89850E9}">
+  <dimension ref="A1:U48"/>
+  <sheetFormatPr defaultColWidth="11.109375" defaultRowHeight="19.5" outlineLevelCol="1" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="4" width="11.109375" style="22"/>
+    <col min="5" max="5" width="14.109375" style="22" customWidth="1"/>
+    <col min="6" max="7" width="11.109375" style="22"/>
+    <col min="8" max="9" width="12.5546875" style="22" customWidth="1"/>
+    <col min="10" max="11" width="11.109375" style="22" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="19" width="11.109375" style="22"/>
+    <col min="20" max="21" width="12.5546875" style="22" customWidth="1"/>
+    <col min="22" max="16384" width="11.109375" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A1" s="22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A3" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A4" s="22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A5" s="22" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A6" s="22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A8" s="22" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A9" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A10" s="24"/>
+      <c r="B10" s="24" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A11" s="24"/>
+      <c r="B11" s="24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="13" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="43"/>
+      <c r="D13" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+      <c r="M13" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="N13" s="45"/>
+      <c r="P13" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="47"/>
+      <c r="R13" s="47"/>
+      <c r="S13" s="47"/>
+      <c r="T13" s="47"/>
+      <c r="U13" s="48"/>
+    </row>
+    <row r="14" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="43"/>
+      <c r="B14" s="43"/>
+      <c r="D14" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="E14" s="44"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="45"/>
+      <c r="M14" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="N14" s="48"/>
+      <c r="P14" s="49"/>
+      <c r="Q14" s="50"/>
+      <c r="R14" s="50"/>
+      <c r="S14" s="50"/>
+      <c r="T14" s="50"/>
+      <c r="U14" s="51"/>
+    </row>
+    <row r="15" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="43"/>
+      <c r="B15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="K15" s="43"/>
+      <c r="M15" s="49"/>
+      <c r="N15" s="51"/>
+      <c r="P15" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q15" s="43"/>
+      <c r="R15" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="S15" s="43"/>
+      <c r="T15" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="U15" s="43"/>
+    </row>
+    <row r="16" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="Q16" s="25"/>
+      <c r="S16" s="25"/>
+      <c r="U16" s="25"/>
+    </row>
+    <row r="17" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B17" s="25"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="G17" s="18"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="18"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="18"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="18"/>
+    </row>
+    <row r="18" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="25"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="I18" s="18"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="18"/>
+      <c r="R18" s="20"/>
+      <c r="S18" s="18"/>
+      <c r="T18" s="20"/>
+      <c r="U18" s="18"/>
+    </row>
+    <row r="19" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="25"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="18"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="18"/>
+      <c r="T19" s="20"/>
+      <c r="U19" s="18"/>
+    </row>
+    <row r="20" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="25"/>
+      <c r="E20" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="F20" s="20"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="18"/>
+      <c r="R20" s="20"/>
+      <c r="S20" s="18"/>
+      <c r="T20" s="20"/>
+      <c r="U20" s="18"/>
+    </row>
+    <row r="21" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="25"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="18"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="18"/>
+      <c r="T21" s="20"/>
+      <c r="U21" s="18"/>
+    </row>
+    <row r="22" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="25"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="N22" s="18"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="18"/>
+      <c r="R22" s="20"/>
+      <c r="S22" s="18"/>
+      <c r="T22" s="20"/>
+      <c r="U22" s="18"/>
+    </row>
+    <row r="23" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B23" s="25"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="18"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="18"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="18"/>
+    </row>
+    <row r="24" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B24" s="25"/>
+      <c r="E24" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="F24" s="20"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="18"/>
+      <c r="R24" s="20"/>
+      <c r="S24" s="18"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="18"/>
+    </row>
+    <row r="25" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="25"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q25" s="18"/>
+      <c r="R25" s="20"/>
+      <c r="S25" s="18"/>
+      <c r="T25" s="20"/>
+      <c r="U25" s="18"/>
+    </row>
+    <row r="26" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="25"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="18"/>
+      <c r="R26" s="20"/>
+      <c r="S26" s="18"/>
+      <c r="T26" s="20"/>
+      <c r="U26" s="18"/>
+    </row>
+    <row r="27" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="25"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="18"/>
+      <c r="R27" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="S27" s="18"/>
+      <c r="T27" s="20"/>
+      <c r="U27" s="18"/>
+    </row>
+    <row r="28" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B28" s="25"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="18"/>
+      <c r="R28" s="20"/>
+      <c r="S28" s="18"/>
+      <c r="T28" s="20"/>
+      <c r="U28" s="18"/>
+    </row>
+    <row r="29" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="25"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="18"/>
+      <c r="R29" s="20"/>
+      <c r="S29" s="18"/>
+      <c r="T29" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="U29" s="18"/>
+    </row>
+    <row r="30" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="25"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="20"/>
+      <c r="N30" s="18"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="18"/>
+      <c r="R30" s="20"/>
+      <c r="S30" s="18"/>
+      <c r="T30" s="20"/>
+      <c r="U30" s="18"/>
+    </row>
+    <row r="31" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B31" s="25"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="18"/>
+      <c r="R31" s="20"/>
+      <c r="S31" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="T31" s="20"/>
+      <c r="U31" s="18"/>
+    </row>
+    <row r="32" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B32" s="25"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="20"/>
+      <c r="M32" s="20"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="18"/>
+      <c r="R32" s="20"/>
+      <c r="S32" s="18"/>
+      <c r="T32" s="20"/>
+      <c r="U32" s="18"/>
+    </row>
+    <row r="33" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B33" s="25"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="20"/>
+      <c r="M33" s="20"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="18"/>
+      <c r="R33" s="20"/>
+      <c r="S33" s="18"/>
+      <c r="T33" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="U33" s="18"/>
+    </row>
+    <row r="34" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B34" s="25"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="20"/>
+      <c r="N34" s="18"/>
+      <c r="O34" s="20"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="R34" s="20"/>
+      <c r="S34" s="18"/>
+      <c r="T34" s="20"/>
+      <c r="U34" s="18"/>
+    </row>
+    <row r="35" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="25"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="20"/>
+      <c r="M35" s="20"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="20"/>
+      <c r="P35" s="20"/>
+      <c r="Q35" s="18"/>
+      <c r="R35" s="20"/>
+      <c r="S35" s="18"/>
+      <c r="T35" s="20"/>
+      <c r="U35" s="18"/>
+    </row>
+    <row r="36" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="25"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="20"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="20"/>
+      <c r="M36" s="20"/>
+      <c r="N36" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="O36" s="20"/>
+      <c r="P36" s="20"/>
+      <c r="Q36" s="18"/>
+      <c r="R36" s="20"/>
+      <c r="S36" s="18"/>
+      <c r="T36" s="20"/>
+      <c r="U36" s="18"/>
+    </row>
+    <row r="37" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B37" s="25"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="20"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="20"/>
+      <c r="M37" s="20"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="20"/>
+      <c r="P37" s="20"/>
+      <c r="Q37" s="18"/>
+      <c r="R37" s="20"/>
+      <c r="S37" s="18"/>
+      <c r="T37" s="20"/>
+      <c r="U37" s="18"/>
+    </row>
+    <row r="38" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B38" s="25"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="20"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="20"/>
+      <c r="M38" s="20"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="20"/>
+      <c r="P38" s="20"/>
+      <c r="Q38" s="18"/>
+      <c r="R38" s="20"/>
+      <c r="S38" s="18"/>
+      <c r="T38" s="20"/>
+      <c r="U38" s="18"/>
+    </row>
+    <row r="39" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B39" s="25"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="20"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="20"/>
+      <c r="M39" s="20"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="20"/>
+      <c r="P39" s="20"/>
+      <c r="Q39" s="18"/>
+      <c r="R39" s="20"/>
+      <c r="S39" s="18"/>
+      <c r="T39" s="20"/>
+      <c r="U39" s="18"/>
+    </row>
+    <row r="40" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="25"/>
+      <c r="E40" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="F40" s="20"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="20"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="20"/>
+      <c r="M40" s="20"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="20"/>
+      <c r="P40" s="20"/>
+      <c r="Q40" s="18"/>
+      <c r="R40" s="20"/>
+      <c r="S40" s="18"/>
+      <c r="T40" s="20"/>
+      <c r="U40" s="18"/>
+    </row>
+    <row r="41" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B41" s="25"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="20"/>
+      <c r="M41" s="20"/>
+      <c r="N41" s="18"/>
+      <c r="O41" s="20"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="18"/>
+      <c r="R41" s="20"/>
+      <c r="S41" s="18"/>
+      <c r="T41" s="20"/>
+      <c r="U41" s="18"/>
+    </row>
+    <row r="42" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B42" s="25"/>
+      <c r="E42" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="F42" s="20"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="20"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="20"/>
+      <c r="M42" s="20"/>
+      <c r="N42" s="18"/>
+      <c r="O42" s="20"/>
+      <c r="P42" s="20"/>
+      <c r="Q42" s="18"/>
+      <c r="R42" s="20"/>
+      <c r="S42" s="18"/>
+      <c r="T42" s="20"/>
+      <c r="U42" s="18"/>
+    </row>
+    <row r="43" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B43" s="25"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="20"/>
+      <c r="K43" s="18"/>
+      <c r="L43" s="20"/>
+      <c r="M43" s="20"/>
+      <c r="N43" s="18"/>
+      <c r="O43" s="20"/>
+      <c r="P43" s="20"/>
+      <c r="Q43" s="18"/>
+      <c r="R43" s="20"/>
+      <c r="S43" s="18"/>
+      <c r="T43" s="20"/>
+      <c r="U43" s="18"/>
+    </row>
+    <row r="44" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B44" s="25"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="K44" s="18"/>
+      <c r="L44" s="20"/>
+      <c r="M44" s="20"/>
+      <c r="N44" s="18"/>
+      <c r="O44" s="20"/>
+      <c r="P44" s="20"/>
+      <c r="Q44" s="18"/>
+      <c r="R44" s="20"/>
+      <c r="S44" s="18"/>
+      <c r="T44" s="20"/>
+      <c r="U44" s="18"/>
+    </row>
+    <row r="45" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B45" s="25"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="18"/>
+      <c r="L45" s="20"/>
+      <c r="M45" s="20"/>
+      <c r="N45" s="18"/>
+      <c r="O45" s="20"/>
+      <c r="P45" s="20"/>
+      <c r="Q45" s="18"/>
+      <c r="R45" s="20"/>
+      <c r="S45" s="18"/>
+      <c r="T45" s="20"/>
+      <c r="U45" s="18"/>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B46" s="25"/>
+      <c r="E46" s="25"/>
+      <c r="G46" s="25"/>
+      <c r="I46" s="25"/>
+      <c r="K46" s="25"/>
+      <c r="N46" s="25"/>
+      <c r="Q46" s="25"/>
+      <c r="S46" s="25"/>
+      <c r="U46" s="25"/>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B47" s="25"/>
+      <c r="E47" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="G47" s="25"/>
+      <c r="I47" s="25"/>
+      <c r="K47" s="25"/>
+      <c r="N47" s="25"/>
+      <c r="Q47" s="25"/>
+      <c r="S47" s="25"/>
+      <c r="U47" s="25"/>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B48" s="25"/>
+      <c r="E48" s="18"/>
+      <c r="G48" s="25"/>
+      <c r="I48" s="25"/>
+      <c r="K48" s="25"/>
+      <c r="N48" s="25"/>
+      <c r="Q48" s="25"/>
+      <c r="S48" s="25"/>
+      <c r="U48" s="25"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="A13:B15"/>
+    <mergeCell ref="D13:K13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="P13:U14"/>
+    <mergeCell ref="D14:E15"/>
+    <mergeCell ref="F14:K14"/>
+    <mergeCell ref="M14:N15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J15:K15"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="27" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D39AED11-B09D-3740-A641-54F04C581F76}">
   <dimension ref="A1:AE103"/>
-  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="20" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="11.109375" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="6" max="6" width="15.69140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.69140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.53515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.69140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.69140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.69140625" customWidth="1"/>
-    <col min="24" max="24" width="10.69140625" customWidth="1"/>
-    <col min="28" max="28" width="10.69140625" customWidth="1"/>
-    <col min="30" max="30" width="10.69140625" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.6640625" customWidth="1"/>
+    <col min="24" max="24" width="10.6640625" customWidth="1"/>
+    <col min="28" max="28" width="10.6640625" customWidth="1"/>
+    <col min="30" max="30" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>79</v>
       </c>
@@ -10100,144 +12202,144 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A10" s="13"/>
       <c r="B10" s="13" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A11" s="13"/>
       <c r="B11" s="13" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.6"/>
-    <row r="13" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="22" t="s">
+    <row r="12" spans="1:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="13" spans="1:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="22"/>
-      <c r="D13" s="22" t="s">
+      <c r="B13" s="27"/>
+      <c r="D13" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="M13" s="22" t="s">
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="M13" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="22"/>
-      <c r="T13" s="22" t="s">
+      <c r="N13" s="27"/>
+      <c r="O13" s="27"/>
+      <c r="P13" s="27"/>
+      <c r="Q13" s="27"/>
+      <c r="R13" s="27"/>
+      <c r="T13" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="U13" s="22"/>
-      <c r="V13" s="22"/>
-      <c r="W13" s="22"/>
-      <c r="X13" s="22"/>
-      <c r="Y13" s="22"/>
-      <c r="Z13" s="22"/>
-      <c r="AA13" s="22"/>
-      <c r="AB13" s="22"/>
-      <c r="AC13" s="22"/>
-      <c r="AD13" s="22"/>
-      <c r="AE13" s="22"/>
-    </row>
-    <row r="14" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="D14" s="22" t="s">
+      <c r="U13" s="27"/>
+      <c r="V13" s="27"/>
+      <c r="W13" s="27"/>
+      <c r="X13" s="27"/>
+      <c r="Y13" s="27"/>
+      <c r="Z13" s="27"/>
+      <c r="AA13" s="27"/>
+      <c r="AB13" s="27"/>
+      <c r="AC13" s="27"/>
+      <c r="AD13" s="27"/>
+      <c r="AE13" s="27"/>
+    </row>
+    <row r="14" spans="1:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="27"/>
+      <c r="B14" s="27"/>
+      <c r="D14" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="E14" s="35"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="37"/>
-      <c r="M14" s="22" t="s">
+      <c r="E14" s="40"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="42"/>
+      <c r="M14" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="N14" s="35"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="37"/>
-      <c r="T14" s="22" t="s">
+      <c r="N14" s="40"/>
+      <c r="O14" s="41"/>
+      <c r="P14" s="41"/>
+      <c r="Q14" s="41"/>
+      <c r="R14" s="42"/>
+      <c r="T14" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="U14" s="35"/>
-      <c r="V14" s="36"/>
-      <c r="W14" s="36"/>
-      <c r="X14" s="36"/>
-      <c r="Y14" s="36"/>
-      <c r="Z14" s="36"/>
-      <c r="AA14" s="36"/>
-      <c r="AB14" s="36"/>
-      <c r="AC14" s="36"/>
-      <c r="AD14" s="36"/>
-      <c r="AE14" s="36"/>
-    </row>
-    <row r="15" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="22"/>
-      <c r="B15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22" t="s">
+      <c r="U14" s="40"/>
+      <c r="V14" s="41"/>
+      <c r="W14" s="41"/>
+      <c r="X14" s="41"/>
+      <c r="Y14" s="41"/>
+      <c r="Z14" s="41"/>
+      <c r="AA14" s="41"/>
+      <c r="AB14" s="41"/>
+      <c r="AC14" s="41"/>
+      <c r="AD14" s="41"/>
+      <c r="AE14" s="41"/>
+    </row>
+    <row r="15" spans="1:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="27"/>
+      <c r="B15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22" t="s">
+      <c r="G15" s="27"/>
+      <c r="H15" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22" t="s">
+      <c r="I15" s="27"/>
+      <c r="J15" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="K15" s="22"/>
-      <c r="M15" s="22"/>
-      <c r="N15" s="22"/>
-      <c r="O15" s="22" t="s">
+      <c r="K15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="P15" s="22"/>
-      <c r="Q15" s="22" t="s">
+      <c r="P15" s="27"/>
+      <c r="Q15" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="22"/>
-      <c r="T15" s="22"/>
-      <c r="U15" s="22"/>
-      <c r="V15" s="22" t="s">
+      <c r="R15" s="27"/>
+      <c r="T15" s="27"/>
+      <c r="U15" s="27"/>
+      <c r="V15" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="W15" s="22"/>
-      <c r="X15" s="22" t="s">
+      <c r="W15" s="27"/>
+      <c r="X15" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="Y15" s="22"/>
-      <c r="Z15" s="38" t="s">
+      <c r="Y15" s="27"/>
+      <c r="Z15" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="AA15" s="39"/>
-      <c r="AB15" s="22" t="s">
+      <c r="AA15" s="55"/>
+      <c r="AB15" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="AC15" s="22"/>
-      <c r="AD15" s="22" t="s">
+      <c r="AC15" s="27"/>
+      <c r="AD15" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="AE15" s="22"/>
-    </row>
-    <row r="16" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="AE15" s="27"/>
+    </row>
+    <row r="16" spans="1:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="5"/>
       <c r="E16" s="5"/>
       <c r="G16" s="5"/>
@@ -10253,7 +12355,7 @@
       <c r="AC16" s="5"/>
       <c r="AE16" s="5"/>
     </row>
-    <row r="17" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="17" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="5"/>
       <c r="E17" s="5"/>
       <c r="G17" s="5"/>
@@ -10272,7 +12374,7 @@
       <c r="AC17" s="5"/>
       <c r="AE17" s="5"/>
     </row>
-    <row r="18" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="18" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="5"/>
       <c r="E18" s="5"/>
       <c r="G18" s="5"/>
@@ -10288,7 +12390,7 @@
       <c r="AC18" s="5"/>
       <c r="AE18" s="5"/>
     </row>
-    <row r="19" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="19" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="5"/>
       <c r="E19" s="5"/>
       <c r="G19" s="5"/>
@@ -10308,7 +12410,7 @@
       <c r="AC19" s="5"/>
       <c r="AE19" s="5"/>
     </row>
-    <row r="20" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="20" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="5"/>
       <c r="E20" s="5"/>
       <c r="G20" s="5"/>
@@ -10324,7 +12426,7 @@
       <c r="AC20" s="5"/>
       <c r="AE20" s="5"/>
     </row>
-    <row r="21" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="21" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="5"/>
       <c r="E21" s="15" t="s">
         <v>90</v>
@@ -10345,7 +12447,7 @@
       <c r="AC21" s="5"/>
       <c r="AE21" s="5"/>
     </row>
-    <row r="22" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="22" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="5"/>
       <c r="E22" s="5"/>
       <c r="G22" s="5"/>
@@ -10361,7 +12463,7 @@
       <c r="AC22" s="5"/>
       <c r="AE22" s="5"/>
     </row>
-    <row r="23" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="23" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="5"/>
       <c r="E23" s="5"/>
       <c r="G23" s="5"/>
@@ -10377,7 +12479,7 @@
       <c r="AC23" s="5"/>
       <c r="AE23" s="5"/>
     </row>
-    <row r="24" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="24" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="5"/>
       <c r="E24" s="5"/>
       <c r="G24" s="5"/>
@@ -10396,7 +12498,7 @@
       <c r="AC24" s="5"/>
       <c r="AE24" s="5"/>
     </row>
-    <row r="25" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="25" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="5"/>
       <c r="E25" s="5"/>
       <c r="G25" s="5"/>
@@ -10412,7 +12514,7 @@
       <c r="AC25" s="5"/>
       <c r="AE25" s="5"/>
     </row>
-    <row r="26" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="26" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="5"/>
       <c r="E26" s="5"/>
       <c r="G26" s="5"/>
@@ -10428,7 +12530,7 @@
       <c r="AC26" s="5"/>
       <c r="AE26" s="5"/>
     </row>
-    <row r="27" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="27" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="5"/>
       <c r="E27" s="15" t="s">
         <v>90</v>
@@ -10449,7 +12551,7 @@
       <c r="AC27" s="5"/>
       <c r="AE27" s="5"/>
     </row>
-    <row r="28" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="28" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="5"/>
       <c r="E28" s="5"/>
       <c r="G28" s="5"/>
@@ -10465,7 +12567,7 @@
       <c r="AC28" s="5"/>
       <c r="AE28" s="5"/>
     </row>
-    <row r="29" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="29" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="5"/>
       <c r="E29" s="5"/>
       <c r="G29" s="5"/>
@@ -10484,7 +12586,7 @@
       <c r="AC29" s="5"/>
       <c r="AE29" s="5"/>
     </row>
-    <row r="30" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="30" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="5"/>
       <c r="E30" s="5"/>
       <c r="G30" s="5"/>
@@ -10500,7 +12602,7 @@
       <c r="AC30" s="5"/>
       <c r="AE30" s="5"/>
     </row>
-    <row r="31" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="31" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="5"/>
       <c r="E31" s="5"/>
       <c r="G31" s="5"/>
@@ -10519,7 +12621,7 @@
       <c r="AC31" s="5"/>
       <c r="AE31" s="5"/>
     </row>
-    <row r="32" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="32" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="5"/>
       <c r="E32" s="5"/>
       <c r="G32" s="5"/>
@@ -10535,7 +12637,7 @@
       <c r="AC32" s="5"/>
       <c r="AE32" s="5"/>
     </row>
-    <row r="33" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="33" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="5"/>
       <c r="E33" s="5"/>
       <c r="G33" s="5"/>
@@ -10554,7 +12656,7 @@
       </c>
       <c r="AE33" s="5"/>
     </row>
-    <row r="34" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="34" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="5"/>
       <c r="E34" s="5"/>
       <c r="G34" s="5"/>
@@ -10571,7 +12673,7 @@
       <c r="AD34" s="14"/>
       <c r="AE34" s="5"/>
     </row>
-    <row r="35" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="35" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B35" s="5"/>
       <c r="E35" s="5"/>
       <c r="G35" s="5"/>
@@ -10588,7 +12690,7 @@
       <c r="AD35" s="14"/>
       <c r="AE35" s="5"/>
     </row>
-    <row r="36" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="36" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="5"/>
       <c r="E36" s="5"/>
       <c r="G36" s="5"/>
@@ -10607,7 +12709,7 @@
       <c r="AC36" s="5"/>
       <c r="AE36" s="5"/>
     </row>
-    <row r="37" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="37" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B37" s="5"/>
       <c r="E37" s="5"/>
       <c r="G37" s="5"/>
@@ -10624,7 +12726,7 @@
       <c r="AC37" s="5"/>
       <c r="AE37" s="5"/>
     </row>
-    <row r="38" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="38" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="5"/>
       <c r="E38" s="5"/>
       <c r="G38" s="5"/>
@@ -10643,7 +12745,7 @@
       <c r="AC38" s="5"/>
       <c r="AE38" s="5"/>
     </row>
-    <row r="39" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="39" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="5"/>
       <c r="E39" s="15"/>
       <c r="G39" s="5"/>
@@ -10663,7 +12765,7 @@
       <c r="AC39" s="5"/>
       <c r="AE39" s="5"/>
     </row>
-    <row r="40" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="40" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="5"/>
       <c r="E40" s="5"/>
       <c r="G40" s="5"/>
@@ -10679,7 +12781,7 @@
       <c r="AC40" s="5"/>
       <c r="AE40" s="5"/>
     </row>
-    <row r="41" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="41" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="5"/>
       <c r="E41" s="5"/>
       <c r="G41" s="5"/>
@@ -10698,7 +12800,7 @@
       </c>
       <c r="AE41" s="5"/>
     </row>
-    <row r="42" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="42" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="5"/>
       <c r="E42" s="5"/>
       <c r="G42" s="5"/>
@@ -10717,7 +12819,7 @@
       </c>
       <c r="AE42" s="5"/>
     </row>
-    <row r="43" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="43" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="5"/>
       <c r="E43" s="5"/>
       <c r="G43" s="5"/>
@@ -10733,7 +12835,7 @@
       <c r="AC43" s="5"/>
       <c r="AE43" s="5"/>
     </row>
-    <row r="44" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="44" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="5"/>
       <c r="E44" s="5"/>
       <c r="G44" s="5"/>
@@ -10749,7 +12851,7 @@
       <c r="AC44" s="5"/>
       <c r="AE44" s="5"/>
     </row>
-    <row r="45" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="45" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="5"/>
       <c r="E45" s="5"/>
       <c r="G45" s="5"/>
@@ -10768,7 +12870,7 @@
       </c>
       <c r="AE45" s="5"/>
     </row>
-    <row r="46" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="46" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="5"/>
       <c r="E46" s="5"/>
       <c r="G46" s="5"/>
@@ -10787,7 +12889,7 @@
       </c>
       <c r="AE46" s="5"/>
     </row>
-    <row r="47" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="47" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="5"/>
       <c r="E47" s="5"/>
       <c r="G47" s="5"/>
@@ -10803,7 +12905,7 @@
       <c r="AC47" s="5"/>
       <c r="AE47" s="5"/>
     </row>
-    <row r="48" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="48" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="5"/>
       <c r="E48" s="5"/>
       <c r="G48" s="5"/>
@@ -10822,7 +12924,7 @@
       <c r="AC48" s="5"/>
       <c r="AE48" s="5"/>
     </row>
-    <row r="49" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="49" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B49" s="5"/>
       <c r="E49" s="5"/>
       <c r="G49" s="5"/>
@@ -10843,7 +12945,7 @@
       <c r="AC49" s="5"/>
       <c r="AE49" s="5"/>
     </row>
-    <row r="50" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="50" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="5"/>
       <c r="E50" s="5"/>
       <c r="G50" s="5"/>
@@ -10859,7 +12961,7 @@
       <c r="AC50" s="5"/>
       <c r="AE50" s="5"/>
     </row>
-    <row r="51" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="51" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="5"/>
       <c r="E51" s="5"/>
       <c r="G51" s="5"/>
@@ -10878,7 +12980,7 @@
       <c r="AC51" s="5"/>
       <c r="AE51" s="5"/>
     </row>
-    <row r="52" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="52" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="5"/>
       <c r="E52" s="5"/>
       <c r="G52" s="5"/>
@@ -10894,7 +12996,7 @@
       <c r="AC52" s="5"/>
       <c r="AE52" s="5"/>
     </row>
-    <row r="53" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="53" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="5"/>
       <c r="E53" s="15"/>
       <c r="G53" s="15" t="s">
@@ -10913,7 +13015,7 @@
       <c r="AC53" s="5"/>
       <c r="AE53" s="5"/>
     </row>
-    <row r="54" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="54" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="5"/>
       <c r="E54" s="5"/>
       <c r="G54" s="5"/>
@@ -10930,7 +13032,7 @@
       <c r="AD54" s="19"/>
       <c r="AE54" s="5"/>
     </row>
-    <row r="55" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="55" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="5"/>
       <c r="E55" s="5"/>
       <c r="G55" s="5"/>
@@ -10946,7 +13048,7 @@
       <c r="AC55" s="5"/>
       <c r="AE55" s="5"/>
     </row>
-    <row r="56" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="56" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="5"/>
       <c r="E56" s="5"/>
       <c r="G56" s="5"/>
@@ -10962,7 +13064,7 @@
       <c r="AC56" s="5"/>
       <c r="AE56" s="5"/>
     </row>
-    <row r="57" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="57" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="5"/>
       <c r="E57" s="5"/>
       <c r="G57" s="5"/>
@@ -10981,7 +13083,7 @@
       </c>
       <c r="AE57" s="5"/>
     </row>
-    <row r="58" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="58" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B58" s="5"/>
       <c r="E58" s="5"/>
       <c r="G58" s="5"/>
@@ -10998,7 +13100,7 @@
       <c r="AD58" s="19"/>
       <c r="AE58" s="5"/>
     </row>
-    <row r="59" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="59" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B59" s="5"/>
       <c r="E59" s="5"/>
       <c r="G59" s="5"/>
@@ -11017,7 +13119,7 @@
       <c r="AC59" s="5"/>
       <c r="AE59" s="5"/>
     </row>
-    <row r="60" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="60" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B60" s="5"/>
       <c r="E60" s="5"/>
       <c r="G60" s="5"/>
@@ -11033,7 +13135,7 @@
       <c r="AC60" s="5"/>
       <c r="AE60" s="5"/>
     </row>
-    <row r="61" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="61" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B61" s="5"/>
       <c r="E61" s="5"/>
       <c r="G61" s="5"/>
@@ -11051,7 +13153,7 @@
       <c r="AC61" s="5"/>
       <c r="AE61" s="5"/>
     </row>
-    <row r="62" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="62" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B62" s="5"/>
       <c r="E62" s="5"/>
       <c r="G62" s="5"/>
@@ -11072,7 +13174,7 @@
       <c r="AC62" s="5"/>
       <c r="AE62" s="5"/>
     </row>
-    <row r="63" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="63" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B63" s="5"/>
       <c r="E63" s="15"/>
       <c r="G63" s="5"/>
@@ -11094,7 +13196,7 @@
       <c r="AC63" s="5"/>
       <c r="AE63" s="5"/>
     </row>
-    <row r="64" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="64" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B64" s="5"/>
       <c r="E64" s="5"/>
       <c r="G64" s="5"/>
@@ -11110,7 +13212,7 @@
       <c r="AC64" s="5"/>
       <c r="AE64" s="5"/>
     </row>
-    <row r="65" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="65" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B65" s="5"/>
       <c r="E65" s="5"/>
       <c r="G65" s="5"/>
@@ -11129,7 +13231,7 @@
       </c>
       <c r="AE65" s="5"/>
     </row>
-    <row r="66" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="66" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B66" s="5"/>
       <c r="E66" s="5"/>
       <c r="G66" s="5"/>
@@ -11148,7 +13250,7 @@
       </c>
       <c r="AE66" s="5"/>
     </row>
-    <row r="67" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="67" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B67" s="5"/>
       <c r="E67" s="5"/>
       <c r="G67" s="5"/>
@@ -11164,7 +13266,7 @@
       <c r="AC67" s="5"/>
       <c r="AE67" s="5"/>
     </row>
-    <row r="68" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="68" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B68" s="5"/>
       <c r="E68" s="5"/>
       <c r="G68" s="5"/>
@@ -11180,7 +13282,7 @@
       <c r="AC68" s="5"/>
       <c r="AE68" s="5"/>
     </row>
-    <row r="69" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="69" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B69" s="5"/>
       <c r="E69" s="5"/>
       <c r="G69" s="5"/>
@@ -11199,7 +13301,7 @@
       </c>
       <c r="AE69" s="5"/>
     </row>
-    <row r="70" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="70" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B70" s="5"/>
       <c r="E70" s="5"/>
       <c r="G70" s="5"/>
@@ -11218,7 +13320,7 @@
       </c>
       <c r="AE70" s="5"/>
     </row>
-    <row r="71" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="71" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B71" s="5"/>
       <c r="E71" s="5"/>
       <c r="G71" s="5"/>
@@ -11234,7 +13336,7 @@
       <c r="AC71" s="5"/>
       <c r="AE71" s="5"/>
     </row>
-    <row r="72" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="72" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B72" s="5"/>
       <c r="E72" s="5"/>
       <c r="G72" s="5"/>
@@ -11253,7 +13355,7 @@
       <c r="AC72" s="5"/>
       <c r="AE72" s="5"/>
     </row>
-    <row r="73" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="73" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B73" s="5"/>
       <c r="E73" s="5"/>
       <c r="G73" s="5"/>
@@ -11274,7 +13376,7 @@
       <c r="AC73" s="5"/>
       <c r="AE73" s="5"/>
     </row>
-    <row r="74" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="74" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B74" s="5"/>
       <c r="E74" s="5"/>
       <c r="G74" s="5"/>
@@ -11290,7 +13392,7 @@
       <c r="AC74" s="5"/>
       <c r="AE74" s="5"/>
     </row>
-    <row r="75" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="75" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B75" s="5"/>
       <c r="E75" s="5"/>
       <c r="G75" s="5"/>
@@ -11309,7 +13411,7 @@
       <c r="AC75" s="5"/>
       <c r="AE75" s="5"/>
     </row>
-    <row r="76" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="76" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B76" s="5"/>
       <c r="E76" s="5"/>
       <c r="G76" s="5"/>
@@ -11325,7 +13427,7 @@
       <c r="AC76" s="5"/>
       <c r="AE76" s="5"/>
     </row>
-    <row r="77" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="77" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B77" s="5"/>
       <c r="E77" s="15"/>
       <c r="G77" s="15" t="s">
@@ -11344,7 +13446,7 @@
       <c r="AC77" s="5"/>
       <c r="AE77" s="5"/>
     </row>
-    <row r="78" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="78" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B78" s="5"/>
       <c r="E78" s="5"/>
       <c r="G78" s="5"/>
@@ -11361,7 +13463,7 @@
       <c r="AD78" s="19"/>
       <c r="AE78" s="5"/>
     </row>
-    <row r="79" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="79" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B79" s="5"/>
       <c r="E79" s="5"/>
       <c r="G79" s="5"/>
@@ -11377,7 +13479,7 @@
       <c r="AC79" s="5"/>
       <c r="AE79" s="5"/>
     </row>
-    <row r="80" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="80" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B80" s="5"/>
       <c r="E80" s="5"/>
       <c r="F80" s="14" t="s">
@@ -11396,7 +13498,7 @@
       <c r="AC80" s="5"/>
       <c r="AE80" s="5"/>
     </row>
-    <row r="81" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="81" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B81" s="5"/>
       <c r="E81" s="5"/>
       <c r="G81" s="5"/>
@@ -11412,7 +13514,7 @@
       <c r="AC81" s="5"/>
       <c r="AE81" s="5"/>
     </row>
-    <row r="82" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="82" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B82" s="5"/>
       <c r="E82" s="5"/>
       <c r="G82" s="5"/>
@@ -11431,7 +13533,7 @@
       <c r="AC82" s="5"/>
       <c r="AE82" s="5"/>
     </row>
-    <row r="83" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="83" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B83" s="5"/>
       <c r="E83" s="5"/>
       <c r="G83" s="5"/>
@@ -11447,7 +13549,7 @@
       <c r="AC83" s="5"/>
       <c r="AE83" s="5"/>
     </row>
-    <row r="84" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="84" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B84" s="5"/>
       <c r="E84" s="5"/>
       <c r="G84" s="5"/>
@@ -11463,7 +13565,7 @@
       <c r="AC84" s="5"/>
       <c r="AE84" s="5"/>
     </row>
-    <row r="85" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="85" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B85" s="5"/>
       <c r="E85" s="5"/>
       <c r="G85" s="15" t="s">
@@ -11484,7 +13586,7 @@
       <c r="AC85" s="5"/>
       <c r="AE85" s="5"/>
     </row>
-    <row r="86" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="86" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B86" s="5"/>
       <c r="E86" s="5"/>
       <c r="G86" s="5"/>
@@ -11500,7 +13602,7 @@
       <c r="AC86" s="5"/>
       <c r="AE86" s="5"/>
     </row>
-    <row r="87" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="87" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B87" s="5"/>
       <c r="E87" s="5"/>
       <c r="G87" s="5"/>
@@ -11519,7 +13621,7 @@
       <c r="AC87" s="5"/>
       <c r="AE87" s="5"/>
     </row>
-    <row r="88" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="88" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B88" s="5"/>
       <c r="E88" s="5"/>
       <c r="G88" s="5"/>
@@ -11535,7 +13637,7 @@
       <c r="AC88" s="5"/>
       <c r="AE88" s="5"/>
     </row>
-    <row r="89" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="89" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B89" s="5"/>
       <c r="E89" s="5"/>
       <c r="G89" s="5"/>
@@ -11554,7 +13656,7 @@
       <c r="AC89" s="5"/>
       <c r="AE89" s="5"/>
     </row>
-    <row r="90" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="90" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B90" s="5"/>
       <c r="E90" s="5"/>
       <c r="G90" s="5"/>
@@ -11570,7 +13672,7 @@
       <c r="AC90" s="5"/>
       <c r="AE90" s="5"/>
     </row>
-    <row r="91" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="91" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B91" s="5"/>
       <c r="E91" s="5"/>
       <c r="G91" s="5"/>
@@ -11589,7 +13691,7 @@
       </c>
       <c r="AE91" s="5"/>
     </row>
-    <row r="92" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="92" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B92" s="5"/>
       <c r="E92" s="5"/>
       <c r="G92" s="5"/>
@@ -11605,7 +13707,7 @@
       <c r="AC92" s="5"/>
       <c r="AE92" s="5"/>
     </row>
-    <row r="93" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="93" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B93" s="5"/>
       <c r="E93" s="5"/>
       <c r="G93" s="5"/>
@@ -11621,7 +13723,7 @@
       <c r="AC93" s="5"/>
       <c r="AE93" s="5"/>
     </row>
-    <row r="94" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="94" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B94" s="5"/>
       <c r="E94" s="15" t="s">
         <v>111</v>
@@ -11639,7 +13741,7 @@
       <c r="AC94" s="5"/>
       <c r="AE94" s="5"/>
     </row>
-    <row r="95" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="95" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B95" s="5"/>
       <c r="E95" s="5"/>
       <c r="G95" s="5"/>
@@ -11655,7 +13757,7 @@
       <c r="AC95" s="5"/>
       <c r="AE95" s="5"/>
     </row>
-    <row r="96" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="96" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B96" s="5"/>
       <c r="E96" s="5"/>
       <c r="G96" s="5"/>
@@ -11674,7 +13776,7 @@
       <c r="AC96" s="5"/>
       <c r="AE96" s="5"/>
     </row>
-    <row r="97" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="97" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B97" s="5"/>
       <c r="E97" s="5"/>
       <c r="G97" s="5"/>
@@ -11690,7 +13792,7 @@
       <c r="AC97" s="5"/>
       <c r="AE97" s="5"/>
     </row>
-    <row r="98" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="98" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B98" s="5"/>
       <c r="E98" s="5"/>
       <c r="G98" s="5"/>
@@ -11706,7 +13808,7 @@
       <c r="AC98" s="5"/>
       <c r="AE98" s="5"/>
     </row>
-    <row r="99" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="99" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B99" s="5"/>
       <c r="E99" s="5"/>
       <c r="G99" s="5"/>
@@ -11727,7 +13829,7 @@
       <c r="AC99" s="5"/>
       <c r="AE99" s="5"/>
     </row>
-    <row r="100" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="100" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B100" s="5"/>
       <c r="E100" s="5"/>
       <c r="G100" s="5"/>
@@ -11743,7 +13845,7 @@
       <c r="AC100" s="5"/>
       <c r="AE100" s="5"/>
     </row>
-    <row r="101" spans="2:31" ht="20" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="101" spans="2:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B101" s="5"/>
       <c r="E101" s="5"/>
       <c r="G101" s="5"/>
@@ -11759,12 +13861,12 @@
       <c r="AC101" s="5"/>
       <c r="AE101" s="5"/>
     </row>
-    <row r="102" spans="2:31" x14ac:dyDescent="0.6">
+    <row r="102" spans="2:31" x14ac:dyDescent="0.4">
       <c r="I102" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="103" spans="2:31" x14ac:dyDescent="0.6">
+    <row r="103" spans="2:31" x14ac:dyDescent="0.4">
       <c r="I103" s="20" t="s">
         <v>114</v>
       </c>
@@ -11797,4 +13899,16 @@
   <pageSetup paperSize="9" scale="23" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05D0810C-6D16-4AE3-859E-2934C302EB4B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="58" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>